--- a/HolidayCalendarService/Template/Teams English.xlsx
+++ b/HolidayCalendarService/Template/Teams English.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicoschreder\Development\adventcalendarapp\HolidayCalendarService\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE10B73D-EC29-4BB8-9A83-91DF3E9C68DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A49C68-70F7-4063-A04F-B7A8EE90DBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="120" windowWidth="16960" windowHeight="15370" xr2:uid="{DA429942-75DC-4399-AA24-F29984099B9A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{DA429942-75DC-4399-AA24-F29984099B9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
   <si>
     <t>publishDate</t>
   </si>
@@ -148,13 +148,70 @@
   </si>
   <si>
     <t>How to work in channels in Microsoft Teams</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/1.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/2.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/3.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/4.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/5.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/7.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/8.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/9.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/10.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/12.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/13.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/14.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/15.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/17.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/18.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/19.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/20.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/22.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Teams%20English/23.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,14 +221,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -194,17 +243,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -545,7 +591,7 @@
   <cols>
     <col min="1" max="1" width="58.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="84.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="105.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -570,6 +616,9 @@
       <c r="B2" s="1">
         <v>44896</v>
       </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
       <c r="D2" t="s">
         <v>4</v>
       </c>
@@ -581,6 +630,9 @@
       <c r="B3" s="1">
         <v>44897</v>
       </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
       <c r="D3" t="s">
         <v>4</v>
       </c>
@@ -592,6 +644,9 @@
       <c r="B4" s="1">
         <v>44898</v>
       </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
@@ -603,6 +658,9 @@
       <c r="B5" s="1">
         <v>44899</v>
       </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
       <c r="D5" t="s">
         <v>4</v>
       </c>
@@ -614,6 +672,9 @@
       <c r="B6" s="1">
         <v>44900</v>
       </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
       <c r="D6" t="s">
         <v>4</v>
       </c>
@@ -625,7 +686,7 @@
       <c r="B7" s="1">
         <v>44901</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
@@ -639,6 +700,9 @@
       <c r="B8" s="1">
         <v>44902</v>
       </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
       <c r="D8" t="s">
         <v>4</v>
       </c>
@@ -650,6 +714,9 @@
       <c r="B9" s="1">
         <v>44903</v>
       </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
       <c r="D9" t="s">
         <v>4</v>
       </c>
@@ -661,6 +728,9 @@
       <c r="B10" s="1">
         <v>44904</v>
       </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
       <c r="D10" t="s">
         <v>4</v>
       </c>
@@ -672,6 +742,9 @@
       <c r="B11" s="1">
         <v>44905</v>
       </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
       <c r="D11" t="s">
         <v>4</v>
       </c>
@@ -683,7 +756,7 @@
       <c r="B12" s="1">
         <v>44906</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
@@ -697,6 +770,9 @@
       <c r="B13" s="1">
         <v>44907</v>
       </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
       <c r="D13" t="s">
         <v>4</v>
       </c>
@@ -708,6 +784,9 @@
       <c r="B14" s="1">
         <v>44908</v>
       </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
       <c r="D14" t="s">
         <v>4</v>
       </c>
@@ -719,6 +798,9 @@
       <c r="B15" s="1">
         <v>44909</v>
       </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
       <c r="D15" t="s">
         <v>4</v>
       </c>
@@ -730,6 +812,9 @@
       <c r="B16" s="1">
         <v>44910</v>
       </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
       <c r="D16" t="s">
         <v>4</v>
       </c>
@@ -741,7 +826,7 @@
       <c r="B17" s="1">
         <v>44911</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>25</v>
       </c>
       <c r="D17" t="s">
@@ -755,6 +840,9 @@
       <c r="B18" s="1">
         <v>44912</v>
       </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
       <c r="D18" t="s">
         <v>4</v>
       </c>
@@ -766,6 +854,9 @@
       <c r="B19" s="1">
         <v>44913</v>
       </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
       <c r="D19" t="s">
         <v>4</v>
       </c>
@@ -777,6 +868,9 @@
       <c r="B20" s="1">
         <v>44914</v>
       </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
       <c r="D20" t="s">
         <v>4</v>
       </c>
@@ -788,6 +882,9 @@
       <c r="B21" s="1">
         <v>44915</v>
       </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
       <c r="D21" t="s">
         <v>4</v>
       </c>
@@ -799,7 +896,7 @@
       <c r="B22" s="1">
         <v>44916</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>33</v>
       </c>
       <c r="D22" t="s">
@@ -813,6 +910,9 @@
       <c r="B23" s="1">
         <v>44917</v>
       </c>
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
       <c r="D23" t="s">
         <v>4</v>
       </c>
@@ -824,6 +924,9 @@
       <c r="B24" s="1">
         <v>44918</v>
       </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
       <c r="D24" t="s">
         <v>4</v>
       </c>
@@ -835,7 +938,7 @@
       <c r="B25" s="1">
         <v>44919</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s">
         <v>35</v>
       </c>
       <c r="D25" t="s">
@@ -844,17 +947,10 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" xr:uid="{9D70A3C8-8198-4E02-9DAC-ECA0CA3B941C}"/>
-    <hyperlink ref="C12" r:id="rId2" xr:uid="{1CE47DA8-ED61-4493-AA88-F050728C301F}"/>
-    <hyperlink ref="C17" r:id="rId3" xr:uid="{0EFE390A-E071-43D4-97A2-C6ACA3BB4D7A}"/>
-    <hyperlink ref="C22" r:id="rId4" xr:uid="{F31A7134-258F-474B-AF28-509F7BE9A040}"/>
-    <hyperlink ref="C25" r:id="rId5" xr:uid="{00A4A920-0DF8-4B26-BBF1-3A8D49A4FF21}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId6"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
